--- a/datebase/datebase.xlsx
+++ b/datebase/datebase.xlsx
@@ -5,12 +5,13 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Desktop\CodeUnity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Desktop\CodeUnity\моё\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D652B21-56F4-4525-95D8-87984A8D56E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C7792C5-1C70-4130-B9CA-C7E0A26C875F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51480" yWindow="3165" windowWidth="16440" windowHeight="28440" xr2:uid="{A7D9A9ED-9A9B-4C52-BF1B-4B8F05CD2EA6}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17190" windowHeight="21000" xr2:uid="{A7D9A9ED-9A9B-4C52-BF1B-4B8F05CD2EA6}"/>
+    <workbookView xWindow="17190" yWindow="0" windowWidth="17205" windowHeight="21000" xr2:uid="{977AC34F-2E5B-4E42-975E-B2A223986AFD}"/>
   </bookViews>
   <sheets>
     <sheet name="схема" sheetId="1" r:id="rId1"/>
@@ -18,7 +19,7 @@
     <sheet name="вопросы" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">связи!$A$6:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">связи!$A$6:$J$6</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="127">
   <si>
     <t>User</t>
   </si>
@@ -311,9 +312,6 @@
     <t>Through-модель</t>
   </si>
   <si>
-    <t>Поля в through</t>
-  </si>
-  <si>
     <t>Нужны ли еще поля</t>
   </si>
   <si>
@@ -341,30 +339,12 @@
     <t>Комментарий</t>
   </si>
   <si>
-    <t xml:space="preserve">зачем это поле в модели </t>
-  </si>
-  <si>
     <t>STATUS_PARTICIPANT</t>
   </si>
   <si>
     <t>нет гостя</t>
   </si>
   <si>
-    <t>ProjectCandidateFilterSkill</t>
-  </si>
-  <si>
-    <t>ProjectCandidateFilterWorkFormat</t>
-  </si>
-  <si>
-    <t>ProjectCandidateFilterSpecialization</t>
-  </si>
-  <si>
-    <t>candidate_filter</t>
-  </si>
-  <si>
-    <t>добавить</t>
-  </si>
-  <si>
     <t>projects</t>
   </si>
   <si>
@@ -380,12 +360,6 @@
     <t>apps:</t>
   </si>
   <si>
-    <t>Модели, написанные руками</t>
-  </si>
-  <si>
-    <t>Дополнительные модели, отражённые в "schema-viewer"</t>
-  </si>
-  <si>
     <t>question_tags</t>
   </si>
   <si>
@@ -419,16 +393,34 @@
     <t>project_skills</t>
   </si>
   <si>
-    <t>CandidateFilter</t>
-  </si>
-  <si>
-    <t>CandidateFilterSkill</t>
-  </si>
-  <si>
-    <t>CandidateFilterWorkFormat</t>
-  </si>
-  <si>
-    <t>CandidateFilterSpecialization</t>
+    <t>Кардинальность</t>
+  </si>
+  <si>
+    <t>M:N</t>
+  </si>
+  <si>
+    <t>N:1</t>
+  </si>
+  <si>
+    <t>Through Type</t>
+  </si>
+  <si>
+    <t>auto</t>
+  </si>
+  <si>
+    <t>explicit</t>
+  </si>
+  <si>
+    <t>Таблицы, созданные Django Auth</t>
+  </si>
+  <si>
+    <t>Промежуточные модели</t>
+  </si>
+  <si>
+    <t>Пользовательские модели</t>
+  </si>
+  <si>
+    <t>Промежуточные таблицы БД (join table)</t>
   </si>
 </sst>
 </file>
@@ -581,16 +573,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
@@ -603,6 +592,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -939,38 +940,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
-        <v>113</v>
+      <c r="A1" s="10" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B3" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>110</v>
-      </c>
-      <c r="K3" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="K3" s="10" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="K5" s="6" t="s">
         <v>65</v>
       </c>
     </row>
@@ -1103,7 +1104,7 @@
       <c r="H13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="K13" s="6" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1145,7 +1146,7 @@
       <c r="E16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="11" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="2" t="s">
@@ -1207,13 +1208,13 @@
       <c r="E20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="G20" s="8"/>
+      <c r="G20" s="7"/>
       <c r="H20" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="16" t="s">
         <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
@@ -1222,7 +1223,7 @@
       <c r="F21" t="s">
         <v>79</v>
       </c>
-      <c r="G21" s="8"/>
+      <c r="G21" s="7"/>
       <c r="H21" s="2" t="s">
         <v>24</v>
       </c>
@@ -1240,7 +1241,7 @@
       <c r="F22" t="s">
         <v>79</v>
       </c>
-      <c r="G22" s="8"/>
+      <c r="G22" s="7"/>
       <c r="H22" s="2" t="s">
         <v>25</v>
       </c>
@@ -1255,8 +1256,8 @@
       <c r="F23" t="s">
         <v>79</v>
       </c>
-      <c r="G23" s="8"/>
-      <c r="H23" s="10" t="s">
+      <c r="G23" s="7"/>
+      <c r="H23" s="9" t="s">
         <v>17</v>
       </c>
       <c r="I23" t="s">
@@ -1264,31 +1265,31 @@
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="G24" s="8"/>
+      <c r="G24" s="7"/>
       <c r="H24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="I24" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="G25" s="8"/>
+      <c r="G25" s="7"/>
       <c r="H25" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="G26" s="8"/>
+      <c r="G26" s="7"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B27" s="2" t="s">
@@ -1297,10 +1298,10 @@
       <c r="C27" t="s">
         <v>78</v>
       </c>
-      <c r="E27" s="13" t="s">
+      <c r="E27" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="G27" s="8"/>
+      <c r="G27" s="7"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B28" s="2" t="s">
@@ -1315,8 +1316,8 @@
       <c r="F28" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G28" s="8"/>
-      <c r="H28" s="12" t="s">
+      <c r="G28" s="7"/>
+      <c r="H28" s="11" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1327,8 +1328,8 @@
       <c r="E29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
       <c r="H29" s="2" t="s">
         <v>21</v>
       </c>
@@ -1345,7 +1346,7 @@
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="14" t="s">
         <v>89</v>
       </c>
       <c r="H31" s="3" t="s">
@@ -1353,10 +1354,10 @@
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B32" s="17" t="s">
+      <c r="B32" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="13" t="s">
+      <c r="E32" s="12" t="s">
         <v>57</v>
       </c>
     </row>
@@ -1387,7 +1388,7 @@
       <c r="F34" t="s">
         <v>78</v>
       </c>
-      <c r="H34" s="12" t="s">
+      <c r="H34" s="11" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1408,10 +1409,10 @@
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="E37" s="13" t="s">
+      <c r="E37" s="12" t="s">
         <v>59</v>
       </c>
       <c r="H37" s="3" t="s">
@@ -1450,7 +1451,7 @@
       <c r="C40" t="s">
         <v>78</v>
       </c>
-      <c r="H40" s="12" t="s">
+      <c r="H40" s="11" t="s">
         <v>83</v>
       </c>
     </row>
@@ -1458,7 +1459,7 @@
       <c r="B41" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" s="14" t="s">
         <v>89</v>
       </c>
       <c r="H41" s="3" t="s">
@@ -1472,7 +1473,7 @@
       <c r="B42" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E42" s="13" t="s">
+      <c r="E42" s="12" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1491,7 +1492,7 @@
       <c r="F44" t="s">
         <v>78</v>
       </c>
-      <c r="H44" s="12" t="s">
+      <c r="H44" s="11" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1504,12 +1505,12 @@
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E46" s="15" t="s">
+      <c r="E46" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="E47" s="13" t="s">
+      <c r="E47" s="12" t="s">
         <v>63</v>
       </c>
     </row>
@@ -1530,105 +1531,114 @@
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="9"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="9"/>
-      <c r="E50" s="9"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9"/>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
-        <v>114</v>
+      <c r="A52" s="19" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B54" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="E54" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="H54" s="12" t="s">
-        <v>115</v>
+      <c r="B54" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="K54" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E55" s="18" t="s">
-        <v>116</v>
-      </c>
-      <c r="H55" s="18" t="s">
-        <v>116</v>
+        <v>107</v>
+      </c>
+      <c r="H55" s="17" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>1</v>
-      </c>
       <c r="H56" s="2" t="s">
         <v>20</v>
       </c>
+      <c r="K56" s="12" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B57" s="16" t="s">
-        <v>122</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>118</v>
+      <c r="B57" s="15" t="s">
+        <v>113</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>56</v>
       </c>
+      <c r="K57" s="17" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K58" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K59" s="3" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B60" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="E60" s="13" t="s">
-        <v>119</v>
+      <c r="B60" s="16" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B61" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>1</v>
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B62" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E62" s="16" t="s">
-        <v>120</v>
+      <c r="K62" s="12" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B63" s="3" t="s">
-        <v>124</v>
+        <v>115</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K64" s="15" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="65" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B65" s="17" t="s">
-        <v>125</v>
+      <c r="B65" s="16" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="66" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B66" s="2" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="67" spans="2:2" x14ac:dyDescent="0.25">
@@ -1637,7 +1647,7 @@
       </c>
     </row>
     <row r="68" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B68" s="16" t="s">
+      <c r="B68" s="15" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1649,20 +1659,23 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A9753A-FD46-4A8F-BCE2-4BA4A7F340F7}">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5703125" customWidth="1"/>
-    <col min="2" max="2" width="25.140625" customWidth="1"/>
-    <col min="3" max="9" width="20.28515625" customWidth="1"/>
+    <col min="2" max="3" width="22.5703125" customWidth="1"/>
+    <col min="4" max="5" width="11.7109375" style="21" customWidth="1"/>
+    <col min="6" max="6" width="22.5703125" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="10" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>78</v>
       </c>
       <c r="B1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>33</v>
@@ -1674,12 +1687,12 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>34</v>
@@ -1689,12 +1702,12 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>51</v>
@@ -1706,12 +1719,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
@@ -1721,7 +1734,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>85</v>
@@ -1729,812 +1742,858 @@
       <c r="C6" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="I6" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" s="5" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J6" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>1</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="D7" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
+      <c r="G7" s="18"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>2</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="D8" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>116</v>
+      </c>
       <c r="I8" s="5"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J8" s="5"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>3</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="D9" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="G9" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>114</v>
+      </c>
       <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J9" s="5"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="D10" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="G10" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>112</v>
+      </c>
       <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="5" t="s">
+      <c r="B11" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="D11" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
       <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J11" s="5"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>6</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="D12" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
       <c r="I12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J12" s="5"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>7</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="B13" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="C13" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>57</v>
+      </c>
       <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J13" s="5"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>8</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="B14" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>61</v>
+      </c>
       <c r="I14" s="5"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J14" s="5"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>9</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="B15" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="H15" s="18" t="s">
+        <v>63</v>
+      </c>
       <c r="I15" s="5"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J15" s="5"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>10</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="B16" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="D16" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
+      <c r="G16" s="18"/>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J16" s="5"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>11</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="B17" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>106</v>
+      </c>
       <c r="I17" s="5"/>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J17" s="5"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>12</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18" s="5"/>
+      <c r="G18" s="18"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J18" s="5"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>13</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="G19" s="5"/>
+      <c r="B19" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="18"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J19" s="5"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>14</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J20" s="5"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>15</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>16</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="5"/>
+      <c r="C22" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>0</v>
+      </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5"/>
       <c r="I22" s="5"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J22" s="5"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>17</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F23" s="5"/>
+      <c r="C23" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J23" s="5"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>18</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
+      <c r="B24" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="18" t="s">
+        <v>0</v>
+      </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J24" s="5"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>19</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="F25" s="5"/>
+      <c r="B25" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="5"/>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J25" s="5"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>20</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="5"/>
+      <c r="B26" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="18" t="s">
+        <v>26</v>
+      </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="5"/>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J26" s="5"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>21</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C27" s="5" t="s">
+      <c r="B27" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="C27" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E27" s="5" t="s">
+      <c r="D27" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F27" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J27" s="5"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>22</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F28" s="5"/>
+      <c r="B28" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>71</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F28" s="18" t="s">
+        <v>65</v>
+      </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J28" s="5"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>23</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F29" s="5"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="18"/>
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J29" s="5"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>24</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F30" s="5"/>
+      <c r="B30" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="18"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J30" s="5"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>25</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-      <c r="F31" s="5"/>
+      <c r="B31" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>33</v>
+      </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J31" s="5"/>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>26</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-      <c r="F32" s="5"/>
-      <c r="G32" s="6"/>
+      <c r="B32" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="G32" s="5"/>
       <c r="H32" s="5"/>
       <c r="I32" s="5"/>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J32" s="5"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>27</v>
       </c>
-      <c r="B33" s="5"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
+      <c r="B33" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>0</v>
+      </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
       <c r="I33" s="5"/>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J33" s="5"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>28</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>103</v>
+      <c r="B34" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F34" s="18" t="s">
+        <v>33</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
-      <c r="I34" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>29</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>104</v>
+      <c r="B35" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>0</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
-      <c r="I35" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>30</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>105</v>
+      <c r="B36" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F36" s="18" t="s">
+        <v>55</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
-      <c r="I36" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>31</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+      <c r="B37" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D37" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>0</v>
+      </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="5"/>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J37" s="5"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>32</v>
       </c>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
+      <c r="B38" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C38" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F38" s="18" t="s">
+        <v>59</v>
+      </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J38" s="5"/>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>33</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F39" s="5"/>
+      <c r="B39" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>0</v>
+      </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
-      <c r="I39" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I39" s="5"/>
+      <c r="J39" s="5"/>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>34</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="C40" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F40" s="5"/>
+      <c r="B40" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="F40" s="18" t="s">
+        <v>34</v>
+      </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
-      <c r="I40" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="5">
-        <v>35</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="5">
-        <v>36</v>
-      </c>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="5">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="5"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="5">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5"/>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="5">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5"/>
-      <c r="C45" s="5"/>
-      <c r="D45" s="5"/>
-      <c r="E45" s="5"/>
-      <c r="F45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5"/>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="5">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A6:I6" xr:uid="{86A9753A-FD46-4A8F-BCE2-4BA4A7F340F7}"/>
+  <autoFilter ref="A6:J6" xr:uid="{86A9753A-FD46-4A8F-BCE2-4BA4A7F340F7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2548,10 +2607,10 @@
   <sheetData>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
